--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-visualization-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-visualization-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Moving Average (Trung bình trượt) giúp lọc bỏ các biến động nhiễu ngắn hạn (noise). Ví dụ, đường trung bình động 12 tháng sẽ cộng doanh thu của 12 tháng gần nhất và chia đều, giúp nhìn rõ xu hướng tăng trưởng thực tế (trend) qua các năm bất chấp sự trồi sụt của mùa vụ.</v>
       </c>
       <c r="F2" t="str">
+        <v>Tự động làm tròn tất cả các con số doanh thu hàng tháng về mức trung bình cộng của cả năm — làm tròn trung bình năm</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Xóa bỏ toàn bộ các tháng có doanh số quá thấp hoặc quá cao ra khỏi biểu đồ — lọc bỏ dữ liệu biến động cực đoan</v>
+      </c>
+      <c r="H2" t="str">
         <v>Vẽ thêm đường trung bình động (Moving Average - ví dụ đường trung bình 3 tháng hoặc 12 tháng) đè lên biểu đồ đường gốc — đường trung bình động (Moving Average)</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Chuyển đổi toàn bộ biểu đồ đường sang biểu đồ tròn để triệt tiêu trục thời gian — triệt tiêu thời gian</v>
       </c>
-      <c r="H2" t="str">
-        <v>Tự động làm tròn tất cả các con số doanh thu hàng tháng về mức trung bình cộng của cả năm — làm tròn trung bình năm</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Xóa bỏ toàn bộ các tháng có doanh số quá thấp hoặc quá cao ra khỏi biểu đồ — lọc bỏ dữ liệu biến động cực đoan</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Đối với dữ liệu khổng lồ, việc gọi DirectQuery quét 500 triệu dòng mỗi lần click filter là thảm họa hiệu năng. Giải pháp chuẩn là tạo các bảng tổng hợp (Aggregated Tables - ví dụ: tổng hợp doanh số theo Ngày-Cửa hàng thay vì lưu từng hóa đơn chi tiết). Trong PowerBI, thiết lập cơ chế tự động định tuyến truy vấn: Nếu người dùng xem tổng quan, PowerBI sẽ lấy từ bảng Aggregation (chạy cực nhanh); nếu người dùng drill-down xem chi tiết hóa đơn, hệ thống mới gọi DirectQuery quét bảng chi tiết.</v>
       </c>
       <c r="F3" t="str">
+        <v>Giảm bớt số lượng màu sắc hiển thị trên các biểu đồ tròn và cột của báo cáo — giảm màu sắc vô nghĩa</v>
+      </c>
+      <c r="G3" t="str">
         <v>Tạo các bảng tổng hợp (Aggregations) ở mức độ cao trong database nguồn, thiết lập cơ chế Dual/Import cho bảng tổng hợp đó trong PowerBI; đồng thời tối ưu hóa Index trong SQL Server — sử dụng bảng tổng hợp và tối ưu hóa index</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
+        <v>Yêu cầu lập trình viên viết code khóa tính năng lọc tương tác (Slicers) của người dùng trên dashboard — khóa tính năng bộ lọc</v>
+      </c>
+      <c r="I3" t="str">
         <v>Chuyển đổi kết nối sang dạng Import Mode và nâng cấp ổ cứng của tất cả máy tính người dùng lên SSD 2TB — nâng cấp phần cứng cục bộ</v>
       </c>
-      <c r="H3" t="str">
-        <v>Giảm bớt số lượng màu sắc hiển thị trên các biểu đồ tròn và cột của báo cáo — giảm màu sắc vô nghĩa</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Yêu cầu lập trình viên viết code khóa tính năng lọc tương tác (Slicers) của người dùng trên dashboard — khóa tính năng bộ lọc</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Radar Chart rất tốt để hiển thị profile năng lực đa chiều (multivariate profile). Tuy nhiên, nó có nhược điểm lớn về mặt UX: Con người rất khó so sánh diện tích của các hình đa giác chồng lên nhau. Thứ tự đặt các trục năng lực xung quanh vòng tròn cũng làm thay đổi hình dáng đa giác, gây hiểu lầm trực quan.</v>
       </c>
       <c r="F4" t="str">
+        <v>Biểu đồ bong bóng (Bubble Chart); hạn chế lớn nhất là không thể hiển thị được các giá trị số nguyên — không hiển thị số nguyên</v>
+      </c>
+      <c r="G4" t="str">
         <v>Biểu đồ radar (Radar / Spider Chart); hạn chế lớn nhất là khó so sánh chính xác diện tích chồng lấn giữa các nhân viên và dễ bị biến dạng trực quan tùy thuộc vào thứ tự sắp xếp các trục — biểu đồ radar và hạn chế diện tích chồng lấn</v>
       </c>
-      <c r="G4" t="str">
-        <v>Biểu đồ bong bóng (Bubble Chart); hạn chế lớn nhất là không thể hiển thị được các giá trị số nguyên — không hiển thị số nguyên</v>
-      </c>
       <c r="H4" t="str">
+        <v>Biểu đồ cột chồng 100% (100% Stacked Bar Chart); hạn chế lớn nhất là bắt buộc tổng các tiêu chí năng lực phải bằng đúng 100 — giới hạn tổng số 100</v>
+      </c>
+      <c r="I4" t="str">
         <v>Biểu đồ bản đồ nhiệt (Heatmap); hạn chế lớn nhất là không thể chạy được trên các thiết bị di động chạy iOS — giới hạn hệ điều hành di động</v>
       </c>
-      <c r="I4" t="str">
-        <v>Biểu đồ cột chồng 100% (100% Stacked Bar Chart); hạn chế lớn nhất là bắt buộc tổng các tiêu chí năng lực phải bằng đúng 100 — giới hạn tổng số 100</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Row Context duyệt qua từng dòng nhưng KHÔNG tự động lọc dữ liệu của các bảng có liên kết. Filter Context là bộ lọc thực tế đang áp dụng lên Data Model. Để chuyển đổi Row Context thành Filter Context (ví dụ để tính tổng doanh thu của khách hàng hiện tại khi duyệt bảng), ta phải bọc công thức trong hàm `CALCULATE` (gọi là Context Transition).</v>
       </c>
       <c r="F5" t="str">
+        <v>Row Context chỉ áp dụng cho dữ liệu kiểu chuỗi; còn Filter Context chỉ áp dụng cho dữ liệu kiểu ngày tháng — phân loại theo kiểu dữ liệu</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Row Context làm tăng tốc độ tải trang; còn Filter Context làm giảm dung lượng file báo cáo — tác động hiệu năng</v>
+      </c>
+      <c r="H5" t="str">
         <v>Row Context áp dụng khi duyệt qua từng dòng của bảng (như trong Calculated Column hoặc các hàm vòng lặp dạng X); Filter Context áp dụng bởi các bộ lọc trên báo cáo (slicers, biểu đồ, hàm CALCULATE) tác động lên tập dữ liệu nạp vào phép tính — phân biệt cơ chế lọc dữ liệu DAX</v>
       </c>
-      <c r="G5" t="str">
-        <v>Row Context chỉ áp dụng cho dữ liệu kiểu chuỗi; còn Filter Context chỉ áp dụng cho dữ liệu kiểu ngày tháng — phân loại theo kiểu dữ liệu</v>
-      </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Row Context do hệ thống tự sinh; còn Filter Context bắt buộc lập trình viên phải khai báo thủ công bằng SQL — phân biệt chủ thể tạo</v>
       </c>
-      <c r="I5" t="str">
-        <v>Row Context làm tăng tốc độ tải trang; còn Filter Context làm giảm dung lượng file báo cáo — tác động hiệu năng</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Alert Fatigue xảy ra khi hệ thống báo động quá nhiều đối với các biến động bình thường (noise). Biểu đồ SPC sử dụng toán thống kê để phân biệt biến động ngẫu nhiên (Common cause variation - không cần báo động) và biến động bất thường (Special cause variation - vượt biên UCL/LCL - bắt buộc phải báo động và xử lý).</v>
       </c>
       <c r="F6" t="str">
+        <v>Thiết kế tất cả các chỉ số trên dashboard đều hiển thị màu đỏ nhấp nháy để bắt buộc nhân viên phải chú ý liên tục — cảnh báo đỏ toàn diện gây nhiễu</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Ẩn toàn bộ các chỉ số cảnh báo đi, khi nào sự cố thực sự xảy ra thì hệ thống tự động khóa màn hình của người dùng — ẩn cảnh báo khóa màn hình</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Yêu cầu hệ thống gửi tin nhắn SMS cảnh báo đến điện thoại của giám đốc bệnh viện cứ sau mỗi 5 phút — gửi SMS liên tục</v>
+      </c>
+      <c r="I6" t="str">
         <v>Thiết kế biểu đồ kiểm soát quy trình bằng thống kê (SPC Chart - Statistical Process Control) với các đường biên giới hạn trên/dưới (UCL/LCL); chỉ kích hoạt cảnh báo đỏ hoặc gửi thông báo khi dữ liệu vượt quá các biên giới hạn thống kê này hoặc có xu hướng lệch biên liên tục — biểu đồ kiểm soát thống kê SPC</v>
       </c>
-      <c r="G6" t="str">
-        <v>Thiết kế tất cả các chỉ số trên dashboard đều hiển thị màu đỏ nhấp nháy để bắt buộc nhân viên phải chú ý liên tục — cảnh báo đỏ toàn diện gây nhiễu</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Ẩn toàn bộ các chỉ số cảnh báo đi, khi nào sự cố thực sự xảy ra thì hệ thống tự động khóa màn hình của người dùng — ẩn cảnh báo khóa màn hình</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Yêu cầu hệ thống gửi tin nhắn SMS cảnh báo đến điện thoại của giám đốc bệnh viện cứ sau mỗi 5 phút — gửi SMS liên tục</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -623,10 +623,10 @@
         <v>Viết trực tiếp trong CALCULATE là viết tắt (syntax sugar), PowerBI sẽ tự động chuyển đổi thành hàm FILTER tối ưu trên các cột; sử dụng hàm FILTER(table, ...) duyệt qua toàn bộ bảng vật lý sẽ rất chậm nếu bảng lớn — tối ưu hóa ngữ cảnh lọc cột vs duyệt bảng</v>
       </c>
       <c r="G7" t="str">
+        <v>FILTER bắt buộc phải trả về kiểu dữ liệu số nguyên; còn CALCULATE bắt buộc phải trả về kiểu dữ liệu boolean — kiểu dữ liệu trả về</v>
+      </c>
+      <c r="H7" t="str">
         <v>FILTER chỉ chạy được trên các bảng có ít hơn 100 dòng; còn viết trực tiếp trong CALCULATE hỗ trợ bảng vô hạn — giới hạn kích thước bảng</v>
-      </c>
-      <c r="H7" t="str">
-        <v>FILTER bắt buộc phải trả về kiểu dữ liệu số nguyên; còn CALCULATE bắt buộc phải trả về kiểu dữ liệu boolean — kiểu dữ liệu trả về</v>
       </c>
       <c r="I7" t="str">
         <v>FILTER chạy nhanh gấp 10 lần so với CALCULATE do không tốn tài nguyên chuyển đổi ngữ cảnh — so sánh tốc độ chạy</v>
@@ -652,19 +652,19 @@
         <v>Sankey Diagram là công cụ hoàn hảo để trực quan hóa dòng chảy (flows) năng lượng, vật liệu hoặc chi phí. Độ rộng của các luồng liên kết (links) thể hiện trực quan lưu lượng, giúp dễ dàng nhận ra các điểm nghẽn (bottlenecks) hoặc thất thoát trong hệ thống.</v>
       </c>
       <c r="F8" t="str">
+        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ theo tọa độ</v>
+      </c>
+      <c r="G8" t="str">
         <v>Biểu đồ Sankey (Sankey Diagram) — trực quan hóa luồng dòng chảy với độ rộng của nhánh tỷ lệ thuận với lưu lượng</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
+        <v>Biểu đồ radar (Radar Chart) — trực quan hóa cấu trúc năng lực đa chiều</v>
+      </c>
+      <c r="I8" t="str">
         <v>Biểu đồ cột chồng 100% (100% Stacked Column Chart) — trực quan hóa tỷ lệ phần trăm phân bổ</v>
       </c>
-      <c r="H8" t="str">
-        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ theo tọa độ</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Biểu đồ radar (Radar Chart) — trực quan hóa cấu trúc năng lực đa chiều</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Các hàm Time Intelligence của DAX hoạt động dựa trên giả định rằng bảng ngày tháng là liên tục (không mất ngày nào kể cả ngày lễ, cuối tuần). Nếu bảng giao dịch (Sales Table) bị mất ngày không có giao dịch, việc gọi các hàm dịch chuyển thời gian (như so sánh cùng kỳ năm ngoái) trực tiếp trên cột ngày của Sales Table sẽ tính toán sai lệch hoặc báo lỗi.</v>
       </c>
       <c r="F9" t="str">
+        <v>Vì nếu không tạo bảng Date độc lập, PowerBI sẽ không cho phép người dùng vẽ biểu đồ đường theo thời gian — giới hạn vẽ biểu đồ</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Để hệ thống tự động mã hóa toàn bộ dữ liệu thời gian tránh sự tấn công của hacker — bảo mật dữ liệu thời gian</v>
+      </c>
+      <c r="H9" t="str">
         <v>Để đảm bảo bảng chứa một chuỗi ngày liên tục không bị ngắt quãng (không có khoảng trống ngày) và có kiểu dữ liệu Datetime chuẩn, làm cơ sở cho các thuật toán dịch chuyển thời gian của DAX hoạt động chính xác — yêu cầu chuỗi ngày liên tục chuẩn hóa</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>Để PowerBI tự động gửi email báo cáo doanh thu vào ngày cuối cùng của mỗi tháng tài chính — tự động gửi báo cáo tháng</v>
       </c>
-      <c r="H9" t="str">
-        <v>Để hệ thống tự động mã hóa toàn bộ dữ liệu thời gian tránh sự tấn công của hacker — bảo mật dữ liệu thời gian</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Vì nếu không tạo bảng Date độc lập, PowerBI sẽ không cho phép người dùng vẽ biểu đồ đường theo thời gian — giới hạn vẽ biểu đồ</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Cộng trực tiếp tiền tệ khác loại (ví dụ 100 USD + 100 VND) là lỗi tài chính sơ đẳng. BA/DA phải thiết kế Data Model quy đổi động dữ liệu tài chính về một đồng tiền báo cáo chung (Reporting Currency) bằng cách nhân với tỷ giá lịch sử tương ứng với ngày phát sinh transaction đó.</v>
       </c>
       <c r="F10" t="str">
+        <v>Chỉ hiển thị báo cáo doanh thu dưới dạng số lượng sản phẩm bán ra thay vì số tiền tài chính — loại bỏ chỉ số tài chính</v>
+      </c>
+      <c r="G10" t="str">
         <v>Thiết kế bảng tỷ giá lịch sử (Exchange Rates Table) theo từng ngày; ở tầng Data Model, viết công thức quy đổi toàn bộ doanh thu từ tiền tệ gốc sang một đồng tiền chuẩn duy nhất (thường là USD hoặc EUR) dựa trên tỷ giá của ngày xảy ra giao dịch — quy đổi tiền tệ theo tỷ giá lịch sử</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Giữ nguyên số tiền gốc của từng quốc gia và cộng tổng trực tiếp chúng lại với nhau để hiển thị con số doanh thu toàn cầu — cộng gộp tiền tệ khác loại sai lệch</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Yêu cầu tất cả các chi nhánh quốc tế phải tự đổi đơn vị tiền tệ sang USD thủ công trên phần mềm của họ trước khi nạp dữ liệu về kho — yêu cầu sửa dữ liệu nguồn</v>
       </c>
-      <c r="I10" t="str">
-        <v>Chỉ hiển thị báo cáo doanh thu dưới dạng số lượng sản phẩm bán ra thay vì số tiền tài chính — loại bỏ chỉ số tài chính</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Drill-down giúp người dùng đi sâu vào các cấp độ phân cấp dữ liệu (Hierarchies) của cùng một visual. Drill-through giúp người dùng chuyển đổi ngữ cảnh từ trang tổng quan (Executive Dashboard) sang trang báo cáo thao tác chi tiết (Operational Report) của đối tượng cụ thể (ví dụ: bấm vào tên 1 khách hàng để xem toàn bộ lịch sử mua hàng của khách đó ở trang khác).</v>
       </c>
       <c r="F11" t="str">
+        <v>Drill-down dùng cho máy tính để bàn; còn Drill-through chỉ dùng được trên điện thoại di động thông minh — phân loại theo thiết bị</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Drill-down tự động xóa dữ liệu lỗi; còn Drill-through tự động nén kích thước của tệp tin báo cáo — cơ chế tự động dữ liệu</v>
+      </c>
+      <c r="H11" t="str">
         <v>Drill-down cho phép chuyển đổi cấp độ phân cấp trong cùng một biểu đồ (như từ Năm xuống Quý, Tháng); Drill-through cho phép người dùng click vào một phần tử biểu đồ để chuyển sang một trang báo cáo khác hiển thị thông tin chi tiết của riêng phần tử đó — phân cấp biểu đồ vs chuyển trang chi tiết</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Drill-down dùng cho máy tính để bàn; còn Drill-through chỉ dùng được trên điện thoại di động thông minh — phân loại theo thiết bị</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Drill-down tự động xóa dữ liệu lỗi; còn Drill-through tự động nén kích thước của tệp tin báo cáo — cơ chế tự động dữ liệu</v>
       </c>
       <c r="I11" t="str">
         <v>Drill-down do lập trình viên thiết kế; còn Drill-through do khách hàng tự cấu hình bằng câu lệnh SQL — phân chia vai trò</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
